--- a/research/traditional_assets/database/data/taiwan/taiwan_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_oilfield_svcs_equip.xlsx
@@ -648,10 +648,10 @@
         <v>0.01878857498880473</v>
       </c>
       <c r="X2">
-        <v>0.09068284877103475</v>
+        <v>0.09066188803816119</v>
       </c>
       <c r="Y2">
-        <v>-0.07189427378223001</v>
+        <v>-0.07187331304935646</v>
       </c>
       <c r="Z2">
         <v>2.095919448860625</v>
@@ -660,10 +660,10 @@
         <v>-0.002630437924555572</v>
       </c>
       <c r="AB2">
-        <v>0.08639156708815374</v>
+        <v>0.0863728102409272</v>
       </c>
       <c r="AC2">
-        <v>-0.08902200501270931</v>
+        <v>-0.08900324816548277</v>
       </c>
       <c r="AD2">
         <v>1179.7</v>
@@ -785,10 +785,10 @@
         <v>0.01878857498880473</v>
       </c>
       <c r="X3">
-        <v>0.09068284877103475</v>
+        <v>0.09066188803816119</v>
       </c>
       <c r="Y3">
-        <v>-0.07189427378223001</v>
+        <v>-0.07187331304935646</v>
       </c>
       <c r="Z3">
         <v>2.095919448860625</v>
@@ -797,10 +797,10 @@
         <v>-0.002630437924555572</v>
       </c>
       <c r="AB3">
-        <v>0.08639156708815374</v>
+        <v>0.0863728102409272</v>
       </c>
       <c r="AC3">
-        <v>-0.08902200501270931</v>
+        <v>-0.08900324816548277</v>
       </c>
       <c r="AD3">
         <v>1179.7</v>
